--- a/data/suggestions.xlsx
+++ b/data/suggestions.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -688,52 +688,52 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>sej0</t>
+          <t>sej1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>s1</t>
+          <t>s5</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>DDAF004</t>
+          <t>Z74.1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CCAM</t>
+          <t>CIM-10</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Angioplastie coronaire avec pose d'endoprothèse</t>
+          <t>Nécessité d'aide pour les soins personnels</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>89</v>
+        <v>61</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>document</t>
+          <t>fiche</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>doc1</t>
+          <t>f1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Pose d'un stent actif mentionnée dans le compte-rendu de coronarographie.</t>
+          <t>Aide partielle pour la toilette mentionnée dans la fiche de liaison infirmière.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>REC-2024-00099</t>
+          <t>REC-2024-00187</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -743,12 +743,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>s1</t>
+          <t>s6</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>J18.1</t>
+          <t>R06.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -758,37 +758,37 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Pneumopathie lobaire, sans précision</t>
+          <t>Dyspnée</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>document</t>
+          <t>observation</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>doc2</t>
+          <t>o1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Foyer de condensation alvéolaire lobaire décrit sur la radiographie thoracique.</t>
+          <t>Dyspnée de repos avec orthopnée décrite dans l'observation clinique d'entrée.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>REC-2024-00234</t>
+          <t>REC-2024-00187</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>sej1</t>
+          <t>sej0</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -798,21 +798,21 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Z96.6</t>
+          <t>DDAF004</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CIM-10</t>
+          <t>CCAM</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Présence d'implant articulaire</t>
+          <t>Angioplastie coronaire avec pose d'endoprothèse</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -826,14 +826,14 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Pose d'une prothèse totale de hanche mentionnée dans le compte-rendu opératoire.</t>
+          <t>Pose d'un stent actif mentionnée dans le compte-rendu de coronarographie.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>REC-2024-00234</t>
+          <t>REC-2024-00099</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -843,12 +843,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>s2</t>
+          <t>s1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>M16.1</t>
+          <t>J18.1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -858,73 +858,273 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Coxarthrose primaire, autre</t>
+          <t>Pneumopathie lobaire, sans précision</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>parcours</t>
+          <t>document</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>pe1</t>
+          <t>doc2</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Hospitalisation programmée pour pose de prothèse de hanche, suggérant une coxarthrose sous-jacente.</t>
+          <t>Foyer de condensation alvéolaire lobaire décrit sur la radiographie thoracique.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>REC-2024-00099</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>sej1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>s2</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>R05</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>CIM-10</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Toux</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>50</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>fiche</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Toux productive en diminution mentionnée dans la fiche de surveillance respiratoire.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>REC-2024-00234</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>sej1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>s1</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Z96.6</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>CIM-10</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Présence d'implant articulaire</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>88</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>document</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>doc1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Pose d'une prothèse totale de hanche mentionnée dans le compte-rendu opératoire.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>REC-2024-00234</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>sej1</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>s2</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>M16.1</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>CIM-10</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Coxarthrose primaire, autre</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>66</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>parcours</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>pe1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Hospitalisation programmée pour pose de prothèse de hanche, suggérant une coxarthrose sous-jacente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>REC-2024-00234</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>sej1</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>s3</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>R52</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>CIM-10</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Douleur, non classée ailleurs</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>58</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>observation</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>o1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Douleur post-opératoire mentionnée dans l'observation clinique du 02/06.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>REC-2024-00234</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
         <is>
           <t>sej0</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>s1</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>M16.1</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>CIM-10</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>Coxarthrose primaire, autre</t>
         </is>
       </c>
-      <c r="G10" t="n">
+      <c r="G14" t="n">
         <v>72</v>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>document</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>doc1</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>Coxarthrose évoluée symptomatique mentionnée dans le compte-rendu de consultation.</t>
         </is>

--- a/data/suggestions.xlsx
+++ b/data/suggestions.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,6 +479,11 @@
           <t>justification</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>regle_id</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -529,6 +534,11 @@
           <t>Le terme « cardiopathie ischémique » a été détecté dans le compte-rendu d'hospitalisation.</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>RG-04</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -579,6 +589,11 @@
           <t>Mention de « insuffisance rénale aiguë sur chronique stade IIIB » dans le CRH, compatible avec un DFG mesuré à 32-44 mL/min.</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>RG-06</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -629,6 +644,11 @@
           <t>Acte identifié dans le parcours de soins le 05/05 (surveillance diurèse).</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>RG-08</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -679,6 +699,11 @@
           <t>Kaliémie à 3.2-3.4 mmol/L en biologie et mention « kaliémie basse à surveiller » dans le courrier de consultation.</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>RG-07</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -729,6 +754,11 @@
           <t>Aide partielle pour la toilette mentionnée dans la fiche de liaison infirmière.</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>RG-10</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -779,6 +809,11 @@
           <t>Dyspnée de repos avec orthopnée décrite dans l'observation clinique d'entrée.</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>RG-11</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -829,6 +864,11 @@
           <t>Pose d'un stent actif mentionnée dans le compte-rendu de coronarographie.</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>RG-09</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -879,6 +919,11 @@
           <t>Foyer de condensation alvéolaire lobaire décrit sur la radiographie thoracique.</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>RG-09</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -929,6 +974,11 @@
           <t>Toux productive en diminution mentionnée dans la fiche de surveillance respiratoire.</t>
         </is>
       </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>RG-10</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -979,6 +1029,11 @@
           <t>Pose d'une prothèse totale de hanche mentionnée dans le compte-rendu opératoire.</t>
         </is>
       </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>RG-09</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1029,6 +1084,11 @@
           <t>Hospitalisation programmée pour pose de prothèse de hanche, suggérant une coxarthrose sous-jacente.</t>
         </is>
       </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>RG-09</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1079,6 +1139,11 @@
           <t>Douleur post-opératoire mentionnée dans l'observation clinique du 02/06.</t>
         </is>
       </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>RG-11</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1127,6 +1192,11 @@
       <c r="J14" t="inlineStr">
         <is>
           <t>Coxarthrose évoluée symptomatique mentionnée dans le compte-rendu de consultation.</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>RG-09</t>
         </is>
       </c>
     </row>

--- a/data/suggestions.xlsx
+++ b/data/suggestions.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,6 +484,11 @@
           <t>regle_id</t>
         </is>
       </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>highlight</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -539,6 +544,11 @@
           <t>RG-04</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>cardiopathie ischémique</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -594,6 +604,11 @@
           <t>RG-06</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>insuffisance rénale aiguë sur chronique stade IIIB</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -649,6 +664,7 @@
           <t>RG-08</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -704,6 +720,11 @@
           <t>RG-07</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>kaliémie basse</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -759,6 +780,11 @@
           <t>RG-10</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Aide partielle pour la toilette</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -814,6 +840,11 @@
           <t>RG-11</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Dyspnée de repos avec orthopnée</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -869,6 +900,11 @@
           <t>RG-09</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>stent actif</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -924,6 +960,11 @@
           <t>RG-09</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Foyer de condensation alvéolaire</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -979,6 +1020,11 @@
           <t>RG-10</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>expectorations en diminution</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1034,6 +1080,11 @@
           <t>RG-09</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>prothèse totale de hanche</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1089,6 +1140,7 @@
           <t>RG-09</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1144,6 +1196,11 @@
           <t>RG-11</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Douleur post-opératoire</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1197,6 +1254,11 @@
       <c r="K14" t="inlineStr">
         <is>
           <t>RG-09</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Coxarthrose évoluée symptomatique</t>
         </is>
       </c>
     </row>

--- a/data/suggestions.xlsx
+++ b/data/suggestions.xlsx
@@ -436,7 +436,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>sejour_key</t>
+          <t>id_sejour</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -498,7 +498,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>sej1</t>
+          <t>ID0000123</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>sej1</t>
+          <t>ID0000123</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>sej1</t>
+          <t>ID0000123</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>sej1</t>
+          <t>ID0000123</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>sej1</t>
+          <t>ID0000123</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -794,7 +794,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>sej1</t>
+          <t>ID0000123</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>sej0</t>
+          <t>ID0000098</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>sej1</t>
+          <t>ID0000201</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>sej1</t>
+          <t>ID0000201</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>sej1</t>
+          <t>ID0000156</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>sej1</t>
+          <t>ID0000156</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>sej1</t>
+          <t>ID0000156</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1210,7 +1210,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>sej0</t>
+          <t>ID0000142</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
